--- a/custody form.xlsx
+++ b/custody form.xlsx
@@ -1148,7 +1148,7 @@
     <col min="7" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
       <c r="D1" s="72" t="s">
